--- a/backend/fms_core/static/submission_templates/Library_preparation_v4_4_0.xlsx
+++ b/backend/fms_core/static/submission_templates/Library_preparation_v4_4_0.xlsx
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">H01</t>
   </si>
   <si>
-    <t xml:space="preserve">Marie-Michelle Simons</t>
+    <t xml:space="preserve">Marie-Michelle Simon</t>
   </si>
   <si>
     <t xml:space="preserve">miRNA NEBNext </t>
